--- a/data/trans_dic/IP11C$urgencias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30,48; 91,05</t>
+          <t>32,31; 91,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,44; 90,68</t>
+          <t>16,72; 90,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,58; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,01; 100,0</t>
+          <t>31,25; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,19; 87,8</t>
+          <t>16,59; 87,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,72; 85,52</t>
+          <t>31,6; 85,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,42; 100,0</t>
+          <t>42,1; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,53; 82,34</t>
+          <t>38,97; 87,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,76; 81,52</t>
+          <t>39,89; 80,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,83; 100,0</t>
+          <t>46,78; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,07; 100,0</t>
+          <t>58,19; 100,0</t>
         </is>
       </c>
     </row>
@@ -856,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,7; 100,0</t>
+          <t>43,08; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 71,72</t>
+          <t>9,67; 64,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,59; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 72,0</t>
+          <t>9,7; 72,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,42; 85,17</t>
+          <t>34,77; 84,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,8; 89,34</t>
+          <t>31,05; 89,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 100,0</t>
+          <t>24,88; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 80,33</t>
+          <t>34,17; 81,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,54; 68,08</t>
+          <t>27,93; 68,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,16; 92,26</t>
+          <t>46,8; 92,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,95; 86,19</t>
+          <t>25,23; 88,52</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 86,19</t>
+          <t>14,34; 85,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,93; 88,63</t>
+          <t>21,77; 89,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,45; 79,92</t>
+          <t>26,43; 79,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,28; 100,0</t>
+          <t>43,24; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,38; 100,0</t>
+          <t>36,68; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,51; 75,2</t>
+          <t>32,33; 76,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,25; 86,55</t>
+          <t>39,16; 84,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44,85; 100,0</t>
+          <t>35,19; 100,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,51; 76,34</t>
+          <t>29,71; 74,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,24; 65,04</t>
+          <t>24,52; 65,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,59; 100,0</t>
+          <t>62,31; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,15; 92,74</t>
+          <t>21,54; 92,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,24; 89,65</t>
+          <t>53,02; 89,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,19; 69,34</t>
+          <t>35,7; 70,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,82; 88,16</t>
+          <t>42,06; 88,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52,07; 100,0</t>
+          <t>46,8; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,51; 78,71</t>
+          <t>46,9; 77,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,56; 61,38</t>
+          <t>35,7; 60,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,69; 89,83</t>
+          <t>58,44; 88,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,4; 94,6</t>
+          <t>52,98; 94,53</t>
         </is>
       </c>
     </row>
@@ -1276,37 +1277,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,58; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,57; 78,22</t>
+          <t>33,63; 78,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,2; 100,0</t>
+          <t>40,56; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69,43; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,97; 88,66</t>
+          <t>47,64; 89,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 76,71</t>
+          <t>28,74; 78,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,28; 100,0</t>
+          <t>47,85; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,51; 90,23</t>
+          <t>49,26; 86,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,22; 72,19</t>
+          <t>40,57; 72,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,58; 93,18</t>
+          <t>54,66; 92,77</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,52; 100,0</t>
+          <t>24,15; 100,0</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,92; 74,14</t>
+          <t>22,58; 75,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,12; 100,0</t>
+          <t>16,11; 100,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,19; 68,3</t>
+          <t>19,36; 67,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>79,25; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,34; 100,0</t>
+          <t>13,78; 100,0</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,88; 73,04</t>
+          <t>48,68; 74,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,07; 58,93</t>
+          <t>37,39; 61,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74,64; 97,1</t>
+          <t>73,62; 97,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,66; 84,29</t>
+          <t>45,78; 84,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,08; 74,44</t>
+          <t>51,34; 74,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,12; 66,75</t>
+          <t>47,23; 65,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,69; 84,75</t>
+          <t>61,57; 84,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,43; 93,92</t>
+          <t>61,6; 93,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>54,19; 71,33</t>
+          <t>53,43; 71,31</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,6; 60,67</t>
+          <t>45,91; 60,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68,57; 86,7</t>
+          <t>70,48; 87,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,36; 85,54</t>
+          <t>62,85; 87,22</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5597</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6065</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8409</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5534</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1892; 5331</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>781; 4242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1097; 3512</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>657; 3477</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2820; 7622</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2746</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1531; 3637</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3825; 8591</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5424; 10931</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3231; 6907</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4159; 7148</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4737</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5476</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5067</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>8254</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5922</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5877</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2602; 6039</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>745; 4989</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2533</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>546; 4083</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3278; 7968</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1833; 5276</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1795; 7213</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3986; 9460</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4785; 11769</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3729; 7343</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2459; 8628</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4325</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3657</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6728</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8176</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5021</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4392</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>542; 3233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1357; 5556</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2277; 6871</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2626; 6074</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2086; 5688</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4006; 9468</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>4819; 10339</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2246; 6384</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6667</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6839</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6942</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10706</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12709</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8646</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6442</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17373</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19548</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>15589</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>9887</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3778; 9429</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3887; 10425</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5009; 8038</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1146; 4913</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7706; 13027</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8660; 17056</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5186; 10853</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3346; 7151</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12781; 21119</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>14321; 24213</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11906; 18058</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6607; 11789</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7491</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5207</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8032</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10082</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15279</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>12177</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3580</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2856</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4459; 10399</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2673; 6590</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5331; 9970</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3891; 10568</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4228; 8835</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1826</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6919; 12206</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10873; 19427</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8431; 14311</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1088; 4503</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1511</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2840</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2043</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2375</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2084; 6978</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>657; 4077</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2182; 7583</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>403; 2925</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>20832</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>24066</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>19644</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>28958</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>40520</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>19726</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>49791</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>64586</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>50036</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>31444</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>16593; 25547</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>18607; 30430</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>16286; 21512</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7852; 14574</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23185; 33682</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>33744; 47105</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>25073; 34505</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>14805; 22556</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>42345; 56512</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>55655; 73195</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>44297; 55181</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>25883; 35922</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$urgencias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Clase-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,31; 91,02</t>
+          <t>28,94; 90,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 90,79</t>
+          <t>16,2; 90,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31,25; 100,0</t>
+          <t>43,05; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 87,8</t>
+          <t>16,19; 87,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 85,4</t>
+          <t>31,74; 85,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,1; 100,0</t>
+          <t>25,29; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38,97; 87,52</t>
+          <t>35,87; 83,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,89; 80,39</t>
+          <t>41,39; 80,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46,78; 100,0</t>
+          <t>45,28; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,19; 100,0</t>
+          <t>51,52; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,08; 100,0</t>
+          <t>44,12; 100,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 64,76</t>
+          <t>9,75; 71,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 72,55</t>
+          <t>7,91; 72,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,77; 84,51</t>
+          <t>28,53; 81,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,05; 89,35</t>
+          <t>30,8; 89,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,88; 100,0</t>
+          <t>27,75; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,17; 81,09</t>
+          <t>34,72; 81,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,93; 68,7</t>
+          <t>28,34; 67,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46,8; 92,15</t>
+          <t>41,43; 92,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,23; 88,52</t>
+          <t>26,7; 85,62</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 85,58</t>
+          <t>0,0; 85,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,77; 89,15</t>
+          <t>21,79; 88,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,43; 79,74</t>
+          <t>26,87; 85,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,24; 100,0</t>
+          <t>43,02; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,68; 100,0</t>
+          <t>36,66; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32,33; 76,4</t>
+          <t>31,84; 76,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,16; 84,01</t>
+          <t>43,78; 88,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,19; 100,0</t>
+          <t>34,75; 100,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,71; 74,15</t>
+          <t>32,18; 78,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,52; 65,76</t>
+          <t>24,44; 65,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,31; 100,0</t>
+          <t>63,05; 100,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 92,35</t>
+          <t>27,47; 92,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>53,02; 89,64</t>
+          <t>48,4; 89,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,7; 70,32</t>
+          <t>34,93; 68,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,06; 88,01</t>
+          <t>42,85; 89,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46,8; 100,0</t>
+          <t>55,27; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,9; 77,5</t>
+          <t>45,87; 76,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,7; 60,37</t>
+          <t>34,59; 61,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,44; 88,65</t>
+          <t>58,25; 89,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,98; 94,53</t>
+          <t>55,19; 94,99</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,63; 78,42</t>
+          <t>34,13; 78,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40,56; 100,0</t>
+          <t>45,8; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>47,64; 89,1</t>
+          <t>47,54; 89,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,74; 78,06</t>
+          <t>35,03; 79,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,85; 100,0</t>
+          <t>43,3; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,26; 86,9</t>
+          <t>50,5; 86,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,57; 72,49</t>
+          <t>39,22; 72,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54,66; 92,77</t>
+          <t>52,74; 93,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,15; 100,0</t>
+          <t>31,94; 100,0</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,58; 75,6</t>
+          <t>21,7; 74,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,11; 100,0</t>
+          <t>17,73; 100,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,36; 67,27</t>
+          <t>19,04; 67,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,78; 100,0</t>
+          <t>13,34; 100,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48,68; 74,95</t>
+          <t>47,85; 74,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,39; 61,15</t>
+          <t>36,08; 59,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,62; 97,24</t>
+          <t>73,77; 97,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,78; 84,98</t>
+          <t>47,07; 85,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,34; 74,58</t>
+          <t>52,77; 74,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,23; 65,93</t>
+          <t>47,14; 65,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,57; 84,73</t>
+          <t>61,89; 84,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>61,6; 93,85</t>
+          <t>63,09; 93,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>53,43; 71,31</t>
+          <t>54,35; 70,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,91; 60,38</t>
+          <t>45,86; 60,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70,48; 87,8</t>
+          <t>69,69; 87,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,22</t>
+          <t>62,85; 87,16</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1892; 5331</t>
+          <t>1695; 5305</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>781; 4242</t>
+          <t>757; 4223</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,17 +1942,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1097; 3512</t>
+          <t>1512; 3512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>657; 3477</t>
+          <t>641; 3466</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2820; 7622</t>
+          <t>2833; 7626</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1531; 3637</t>
+          <t>920; 3637</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3825; 8591</t>
+          <t>3521; 8200</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5424; 10931</t>
+          <t>5628; 10970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3231; 6907</t>
+          <t>3127; 6907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4159; 7148</t>
+          <t>3682; 7148</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2602; 6039</t>
+          <t>2664; 6039</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>745; 4989</t>
+          <t>751; 5539</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2155,42 +2155,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>546; 4083</t>
+          <t>445; 4058</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3278; 7968</t>
+          <t>2690; 7646</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1833; 5276</t>
+          <t>1818; 5271</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1795; 7213</t>
+          <t>2002; 7213</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3986; 9460</t>
+          <t>4051; 9471</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4785; 11769</t>
+          <t>4855; 11597</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3729; 7343</t>
+          <t>3301; 7334</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2459; 8628</t>
+          <t>2602; 8345</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>542; 3233</t>
+          <t>0; 3228</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1357; 5556</t>
+          <t>1358; 5517</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2277; 6871</t>
+          <t>2315; 7351</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2626; 6074</t>
+          <t>2613; 6074</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2086; 5688</t>
+          <t>2085; 5688</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4006; 9468</t>
+          <t>3946; 9448</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4819; 10339</t>
+          <t>5388; 10872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2246; 6384</t>
+          <t>2219; 6384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3778; 9429</t>
+          <t>4092; 10018</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3887; 10425</t>
+          <t>3874; 10311</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5009; 8038</t>
+          <t>5068; 8038</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1146; 4913</t>
+          <t>1461; 4923</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7706; 13027</t>
+          <t>7034; 13028</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8660; 17056</t>
+          <t>8474; 16598</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5186; 10853</t>
+          <t>5285; 11009</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3346; 7151</t>
+          <t>3952; 7151</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12781; 21119</t>
+          <t>12498; 20811</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14321; 24213</t>
+          <t>13875; 24599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11906; 18058</t>
+          <t>11866; 18259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6607; 11789</t>
+          <t>6883; 11846</t>
         </is>
       </c>
     </row>
@@ -2764,12 +2764,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4459; 10399</t>
+          <t>4526; 10370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2673; 6590</t>
+          <t>3018; 6590</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5331; 9970</t>
+          <t>5319; 9967</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3891; 10568</t>
+          <t>4743; 10703</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4228; 8835</t>
+          <t>3825; 8835</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6919; 12206</t>
+          <t>7093; 12167</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10873; 19427</t>
+          <t>10509; 19480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8431; 14311</t>
+          <t>8135; 14381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1088; 4503</t>
+          <t>1438; 4503</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2084; 6978</t>
+          <t>2003; 6864</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>657; 4077</t>
+          <t>723; 4077</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2182; 7583</t>
+          <t>2146; 7645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>403; 2925</t>
+          <t>390; 2925</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16593; 25547</t>
+          <t>16310; 25254</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18607; 30430</t>
+          <t>17958; 29809</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16286; 21512</t>
+          <t>16319; 21471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7852; 14574</t>
+          <t>8073; 14610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23185; 33682</t>
+          <t>23831; 33691</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33744; 47105</t>
+          <t>33680; 46791</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25073; 34505</t>
+          <t>25204; 34525</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14805; 22556</t>
+          <t>15164; 22468</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>42345; 56512</t>
+          <t>43070; 56153</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55655; 73195</t>
+          <t>55595; 73290</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44297; 55181</t>
+          <t>43799; 54793</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25883; 35922</t>
+          <t>25886; 35896</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$urgencias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>52,36%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62,71%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>86,5%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>68,16%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>60,19%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>87,99%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>52,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,94; 90,57</t>
+          <t>16,19; 87,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,2; 90,36</t>
+          <t>32,72; 85,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 100,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20,74; 100,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30,48; 91,05</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,44; 90,68</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>43,05; 100,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16,19; 87,54</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,74; 85,45</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,29; 100,0</t>
+          <t>33,05; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,87; 83,53</t>
+          <t>36,53; 82,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,39; 80,67</t>
+          <t>39,76; 81,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,28; 100,0</t>
+          <t>42,83; 100,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,52; 100,0</t>
+          <t>55,64; 100,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>58,08%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>65,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67,97%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>78,44%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,05%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>31,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>58,08%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>59,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,12; 100,0</t>
+          <t>8,84; 72,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 71,9</t>
+          <t>31,42; 85,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>30,8; 89,34</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22,55; 100,0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>44,7; 100,0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,11; 71,72</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,91; 72,1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,53; 81,1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,8; 89,28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27,75; 100,0</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,72; 81,18</t>
+          <t>30,95; 80,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,34; 67,69</t>
+          <t>31,54; 68,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,43; 92,04</t>
+          <t>44,16; 92,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,7; 85,62</t>
+          <t>24,76; 85,24</t>
         </is>
       </c>
     </row>
@@ -929,37 +929,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77,81%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>76,04%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>49,9%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>55,36%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>56,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>77,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -997,39 +997,39 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,43</t>
+          <t>31,45; 79,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,79; 88,53</t>
+          <t>43,28; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>37,38; 100,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14,95; 86,19</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,93; 88,63</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>26,87; 85,32</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>43,02; 100,0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>36,66; 100,0</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1037,17 +1037,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,84; 76,24</t>
+          <t>31,51; 75,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43,78; 88,35</t>
+          <t>43,25; 86,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,75; 100,0</t>
+          <t>44,85; 100,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>89,9%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>52,43%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>43,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>86,37%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,11%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,18; 78,79</t>
+          <t>50,24; 89,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,44; 65,04</t>
+          <t>36,19; 69,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,05; 100,0</t>
+          <t>44,82; 88,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,47; 92,54</t>
+          <t>51,38; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,4; 89,64</t>
+          <t>30,51; 76,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,93; 68,43</t>
+          <t>23,24; 65,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,85; 89,27</t>
+          <t>56,59; 100,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55,27; 100,0</t>
+          <t>27,27; 94,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,87; 76,37</t>
+          <t>47,51; 78,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,59; 61,33</t>
+          <t>34,56; 61,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58,25; 89,63</t>
+          <t>57,69; 89,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,19; 94,99</t>
+          <t>51,37; 94,75</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1214,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>57,53%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>78,89%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>71,78%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>56,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>79,02%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>71,78%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>57,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>78,89%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>49,47%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>71,78%</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>57,02%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42,97; 88,66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28,98; 76,71</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48,28; 100,0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>34,13; 78,21</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>45,8; 100,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,58; 100,0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,57; 78,22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,2; 100,0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47,54; 89,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,03; 79,06</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,3; 100,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50,5; 86,62</t>
+          <t>48,51; 90,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,22; 72,69</t>
+          <t>40,22; 72,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52,74; 93,23</t>
+          <t>54,58; 93,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,94; 100,0</t>
+          <t>29,11; 100,0</t>
         </is>
       </c>
     </row>
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45,78%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>52,84%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>34,01%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>40,5%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>42,16%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>67,15%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>67,15%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16,92; 74,14</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>15,12; 100,0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>20,19; 68,3</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>21,7; 74,37</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>17,73; 100,0</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>19,04; 67,82</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,34; 100,0</t>
+          <t>13,25; 100,0</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>61,12%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>48,36%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>88,8%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>56,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,85; 74,09</t>
+          <t>51,08; 74,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36,08; 59,9</t>
+          <t>47,12; 66,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,77; 97,05</t>
+          <t>61,69; 84,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,07; 85,19</t>
+          <t>60,56; 93,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,77; 74,6</t>
+          <t>47,88; 73,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,14; 65,49</t>
+          <t>36,07; 58,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,89; 84,78</t>
+          <t>74,64; 97,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>63,09; 93,49</t>
+          <t>48,84; 85,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>54,35; 70,86</t>
+          <t>54,19; 71,33</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,86; 60,46</t>
+          <t>45,6; 60,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69,69; 87,18</t>
+          <t>68,57; 86,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,16</t>
+          <t>61,46; 85,56</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5597</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3992</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2813</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4162</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5597</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6018</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1695; 5305</t>
+          <t>641; 3477</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>757; 4223</t>
+          <t>2920; 7632</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 2746</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>696; 3355</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1785; 5333</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>721; 4237</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1512; 3512</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>641; 3466</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2833; 7626</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2746</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>920; 3637</t>
+          <t>1151; 3482</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3521; 8200</t>
+          <t>3586; 8082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5628; 10970</t>
+          <t>5407; 11085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3127; 6907</t>
+          <t>2958; 6907</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3682; 7148</t>
+          <t>3804; 6837</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5476</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3858</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4566</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4737</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2778</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5476</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>919</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5485</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2664; 6039</t>
+          <t>498; 4052</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>751; 5539</t>
+          <t>2962; 8030</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>1818; 5275</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1515; 6718</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2699; 6039</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>702; 5525</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2533</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>445; 4058</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2690; 7646</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1818; 5271</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2002; 7213</t>
+          <t>0; 2569</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4051; 9471</t>
+          <t>3611; 9372</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4855; 11597</t>
+          <t>5404; 11664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3301; 7334</t>
+          <t>3518; 7351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2602; 8345</t>
+          <t>2299; 7916</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4843</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4325</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3450</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4843</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4325</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>766</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4316</t>
         </is>
       </c>
     </row>
@@ -2343,39 +2343,39 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3228</t>
+          <t>2710; 6886</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1358; 5517</t>
+          <t>2629; 6074</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>2126; 5688</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>565; 3256</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1367; 5524</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2315; 7351</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2613; 6074</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2085; 5688</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -2383,17 +2383,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3946; 9448</t>
+          <t>3905; 9320</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5388; 10872</t>
+          <t>5322; 10651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2219; 6384</t>
+          <t>2863; 6384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10706</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12709</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8646</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5743</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6667</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6839</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6942</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3445</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10706</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12709</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8646</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>9187</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4092; 10018</t>
+          <t>7301; 13029</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3874; 10311</t>
+          <t>8778; 16820</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5068; 8038</t>
+          <t>5527; 10872</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1461; 4923</t>
+          <t>3283; 6389</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7034; 13028</t>
+          <t>3879; 9708</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8474; 16598</t>
+          <t>3685; 10311</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5285; 11009</t>
+          <t>4549; 8038</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3952; 7151</t>
+          <t>1419; 4912</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12498; 20811</t>
+          <t>12947; 21449</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13875; 24599</t>
+          <t>13862; 24618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11866; 18259</t>
+          <t>11753; 18298</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6883; 11846</t>
+          <t>5956; 10984</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8032</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6970</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2050</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7491</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>5207</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8032</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7788</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6970</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3412</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>4809; 9921</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4526; 10370</t>
+          <t>3923; 10385</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3018; 6590</t>
+          <t>4266; 8835</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0; 1783</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>616; 2856</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4187; 10372</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3045; 6590</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5319; 9967</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4743; 10703</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3825; 8835</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0; 1826</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7093; 12167</t>
+          <t>6813; 12674</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10509; 19480</t>
+          <t>10779; 19344</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8135; 14381</t>
+          <t>8418; 14374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1438; 4503</t>
+          <t>1272; 4369</t>
         </is>
       </c>
     </row>
@@ -2836,37 +2836,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1501</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4225</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5220</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1542</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1562; 6843</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
           <t>0; 2840</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>0; 2043</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>0; 2375</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2577</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>616; 4077</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2276; 7700</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2003; 6864</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>723; 4077</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2146; 7645</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>390; 2925</t>
+          <t>402; 3032</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>28958</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>40520</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>20832</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>24066</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>19644</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>11718</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>28958</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>40520</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>30392</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>29960</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16310; 25254</t>
+          <t>23070; 33619</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17958; 29809</t>
+          <t>33666; 47693</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16319; 21471</t>
+          <t>25123; 34515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8073; 14610</t>
+          <t>13475; 20795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23831; 33691</t>
+          <t>16321; 24896</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33680; 46791</t>
+          <t>17953; 29325</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25204; 34525</t>
+          <t>16512; 21481</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15164; 22468</t>
+          <t>8392; 14651</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>43070; 56153</t>
+          <t>42943; 56532</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55595; 73290</t>
+          <t>55277; 73543</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43799; 54793</t>
+          <t>43092; 54488</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25886; 35896</t>
+          <t>24237; 33742</t>
         </is>
       </c>
     </row>
